--- a/apps/web/public/importmallar/importmall-kundkontakter.xlsx
+++ b/apps/web/public/importmallar/importmall-kundkontakter.xlsx
@@ -82,7 +82,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt med en varning.</t>
+          <t xml:space="preserve">Max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt på en ny post och orört på en befintlig, med en varning.</t>
         </r>
       </text>
     </comment>
@@ -149,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -158,6 +158,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -169,14 +170,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1" style="4"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1" style="4"/>
+    <col min="5" max="5" width="16" customWidth="1" style="4"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1" style="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -254,66 +255,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kundnummer</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Numret på en kund som redan finns i kundregistret — importera kunderna först.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kontaktperson</t>
+          <t xml:space="preserve">Kundnummer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -323,41 +309,41 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kontaktens namn, max 255 tecken. Finns redan en kontakt med samma namn på kunden (skiftlägesokänsligt) hoppas raden över — befintliga kontakter uppdateras aldrig — och samma namn två gånger i filen importeras en gång.</t>
+          <t xml:space="preserve">Numret på en kund som redan finns i kundregistret — importera kunderna först.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Andersson</t>
+          <t xml:space="preserve">1001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Förvald</t>
+          <t xml:space="preserve">Kontaktperson</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej. Ja gör kontakten till kundens huvudkontakt; har kunden redan en importeras kontakten som vanlig kontakt med en varning.</t>
+          <t xml:space="preserve">Kontaktens namn, max 255 tecken. Finns redan en kontakt med samma namn på kunden (skiftlägesokänsligt) hoppas raden över — befintliga kontakter uppdateras aldrig — och samma namn två gånger i filen importeras en gång.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Anna Andersson</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telefon</t>
+          <t xml:space="preserve">Förvald</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -367,19 +353,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 50 tecken.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej. Ja gör kontakten till kundens huvudkontakt; har kunden redan en importeras kontakten som vanlig kontakt med en varning.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010-200 10 11</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobiltelefon</t>
+          <t xml:space="preserve">Telefon</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -394,14 +380,14 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">070-000 00 01</t>
+          <t xml:space="preserve">010-200 10 11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-post</t>
+          <t xml:space="preserve">Mobiltelefon</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -411,19 +397,19 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt med en varning.</t>
+          <t xml:space="preserve">Max 50 tecken.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">anna@example.com</t>
+          <t xml:space="preserve">070-000 00 01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anmärkning</t>
+          <t xml:space="preserve">E-post</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -433,32 +419,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fritext om kontakten.</t>
+          <t xml:space="preserve">Max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt på en ny post och orört på en befintlig, med en varning.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beställer för köket</t>
+          <t xml:space="preserve">anna@example.com</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Anmärkning</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fritext om kontakten.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beställer för köket</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Faxnummer</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nej</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Max 50 tecken. Kontakten har inget eget faxfält — numret läggs i anmärkningen som Fax 010-200 10 19.</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">010-200 10 19</t>
         </is>
